--- a/excel/E2E_Report.xlsx
+++ b/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="172">
   <si>
     <t>Metric</t>
   </si>
@@ -25,13 +25,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>3/8/2026, 9:43:29 am</t>
+    <t>7/8/2026, 9:16:23 pm</t>
   </si>
   <si>
     <t>Environment</t>
   </si>
   <si>
-    <t>http://localhost:4173/CareBridge/</t>
+    <t>http://localhost:4173/</t>
   </si>
   <si>
     <t>Target Browser</t>
@@ -61,13 +61,13 @@
     <t>Pass Percentage</t>
   </si>
   <si>
-    <t>17.39%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>230 seconds</t>
+    <t>187 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -94,7 +94,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>TC-6541</t>
+    <t>TC-2809</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite</t>
@@ -106,196 +106,205 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>9:39:40 am</t>
-  </si>
-  <si>
-    <t>9:39:45 am</t>
+    <t>9:13:17 pm</t>
+  </si>
+  <si>
+    <t>9:13:22 pm</t>
   </si>
   <si>
     <t>5s</t>
   </si>
   <si>
-    <t>TC-9820</t>
+    <t>TC-8857</t>
   </si>
   <si>
     <t>AUTH-002: Validate login with empty password field</t>
   </si>
   <si>
-    <t>9:39:49 am</t>
+    <t>9:13:27 pm</t>
   </si>
   <si>
     <t>4s</t>
   </si>
   <si>
-    <t>TC-7230</t>
+    <t>TC-3871</t>
   </si>
   <si>
     <t>AUTH-003: Validate login with invalid credentials</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>9:39:59 am</t>
+    <t>9:13:31 pm</t>
+  </si>
+  <si>
+    <t>TC-1785</t>
+  </si>
+  <si>
+    <t>AUTH-004: Validate successful Patient authentication flow</t>
+  </si>
+  <si>
+    <t>9:13:35 pm</t>
+  </si>
+  <si>
+    <t>TC-5624</t>
+  </si>
+  <si>
+    <t>AUTH-005: Validate Patient logout flow</t>
+  </si>
+  <si>
+    <t>9:13:40 pm</t>
+  </si>
+  <si>
+    <t>TC-1156</t>
+  </si>
+  <si>
+    <t>AUTH-006: Validate session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>9:13:48 pm</t>
+  </si>
+  <si>
+    <t>7s</t>
+  </si>
+  <si>
+    <t>TC-8978</t>
+  </si>
+  <si>
+    <t>Dynamic Form Validation &amp; Route Discovery Suite</t>
+  </si>
+  <si>
+    <t>FORM-DYN-001: Validate discovered React routes configuration exists</t>
+  </si>
+  <si>
+    <t>9:13:50 pm</t>
+  </si>
+  <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>TC-7147</t>
+  </si>
+  <si>
+    <t>FORM-DYN-002: Dynamic email input format validation on Signup form</t>
+  </si>
+  <si>
+    <t>9:14:06 pm</t>
+  </si>
+  <si>
+    <t>16s</t>
+  </si>
+  <si>
+    <t>TC-1589</t>
+  </si>
+  <si>
+    <t>FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
+  </si>
+  <si>
+    <t>9:14:10 pm</t>
+  </si>
+  <si>
+    <t>TC-7669</t>
+  </si>
+  <si>
+    <t>FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
+  </si>
+  <si>
+    <t>9:14:18 pm</t>
+  </si>
+  <si>
+    <t>8s</t>
+  </si>
+  <si>
+    <t>TC-7949</t>
+  </si>
+  <si>
+    <t>FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
+  </si>
+  <si>
+    <t>9:14:26 pm</t>
+  </si>
+  <si>
+    <t>TC-3681</t>
+  </si>
+  <si>
+    <t>FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
+  </si>
+  <si>
+    <t>9:14:35 pm</t>
+  </si>
+  <si>
+    <t>9s</t>
+  </si>
+  <si>
+    <t>TC-3095</t>
+  </si>
+  <si>
+    <t>FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
+  </si>
+  <si>
+    <t>9:14:46 pm</t>
+  </si>
+  <si>
+    <t>11s</t>
+  </si>
+  <si>
+    <t>TC-5947</t>
+  </si>
+  <si>
+    <t>End-to-End Multi-Role Healthcare Workflow Suite</t>
+  </si>
+  <si>
+    <t>E2E-001: Execute complete End-to-End patient consultation workflow</t>
+  </si>
+  <si>
+    <t>9:15:24 pm</t>
+  </si>
+  <si>
+    <t>38s</t>
+  </si>
+  <si>
+    <t>TC-1356</t>
+  </si>
+  <si>
+    <t>Navigation &amp; Internal Routing Validation Suite</t>
+  </si>
+  <si>
+    <t>NAV-001: Validate navigation through all Patient workspace links</t>
+  </si>
+  <si>
+    <t>9:15:33 pm</t>
+  </si>
+  <si>
+    <t>TC-5919</t>
+  </si>
+  <si>
+    <t>NAV-002: Validate navigation through Doctor workspace tabs</t>
+  </si>
+  <si>
+    <t>9:15:40 pm</t>
+  </si>
+  <si>
+    <t>TC-6737</t>
+  </si>
+  <si>
+    <t>NAV-003: Validate navigation through Operations workspace tabs</t>
+  </si>
+  <si>
+    <t>9:15:48 pm</t>
+  </si>
+  <si>
+    <t>TC-7552</t>
+  </si>
+  <si>
+    <t>NAV-004: Validate browser refresh, back, and forward navigation</t>
+  </si>
+  <si>
+    <t>9:15:57 pm</t>
   </si>
   <si>
     <t>10s</t>
   </si>
   <si>
-    <t>TC-6856</t>
-  </si>
-  <si>
-    <t>AUTH-004: Validate successful Patient authentication flow</t>
-  </si>
-  <si>
-    <t>9:40:11 am</t>
-  </si>
-  <si>
-    <t>11s</t>
-  </si>
-  <si>
-    <t>TC-8861</t>
-  </si>
-  <si>
-    <t>AUTH-005: Validate Patient logout flow</t>
-  </si>
-  <si>
-    <t>9:40:23 am</t>
-  </si>
-  <si>
-    <t>TC-4824</t>
-  </si>
-  <si>
-    <t>AUTH-006: Validate session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>9:40:34 am</t>
-  </si>
-  <si>
-    <t>TC-5821</t>
-  </si>
-  <si>
-    <t>Dynamic Form Validation &amp; Route Discovery Suite</t>
-  </si>
-  <si>
-    <t>FORM-DYN-001: Validate discovered React routes configuration exists</t>
-  </si>
-  <si>
-    <t>9:40:36 am</t>
-  </si>
-  <si>
-    <t>1s</t>
-  </si>
-  <si>
-    <t>TC-9891</t>
-  </si>
-  <si>
-    <t>FORM-DYN-002: Dynamic email input format validation on Signup form</t>
-  </si>
-  <si>
-    <t>9:40:47 am</t>
-  </si>
-  <si>
-    <t>TC-6655</t>
-  </si>
-  <si>
-    <t>FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
-  </si>
-  <si>
-    <t>9:40:59 am</t>
-  </si>
-  <si>
-    <t>12s</t>
-  </si>
-  <si>
-    <t>TC-3593</t>
-  </si>
-  <si>
-    <t>FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
-  </si>
-  <si>
-    <t>9:41:11 am</t>
-  </si>
-  <si>
-    <t>TC-6175</t>
-  </si>
-  <si>
-    <t>FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
-  </si>
-  <si>
-    <t>9:41:23 am</t>
-  </si>
-  <si>
-    <t>TC-7572</t>
-  </si>
-  <si>
-    <t>FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
-  </si>
-  <si>
-    <t>9:41:35 am</t>
-  </si>
-  <si>
-    <t>TC-3912</t>
-  </si>
-  <si>
-    <t>FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
-  </si>
-  <si>
-    <t>9:41:46 am</t>
-  </si>
-  <si>
-    <t>TC-1591</t>
-  </si>
-  <si>
-    <t>End-to-End Multi-Role Healthcare Workflow Suite</t>
-  </si>
-  <si>
-    <t>E2E-001: Execute complete End-to-End patient consultation workflow</t>
-  </si>
-  <si>
-    <t>9:41:58 am</t>
-  </si>
-  <si>
-    <t>TC-7538</t>
-  </si>
-  <si>
-    <t>Navigation &amp; Internal Routing Validation Suite</t>
-  </si>
-  <si>
-    <t>NAV-001: Validate navigation through all Patient workspace links</t>
-  </si>
-  <si>
-    <t>9:42:10 am</t>
-  </si>
-  <si>
-    <t>TC-4080</t>
-  </si>
-  <si>
-    <t>NAV-002: Validate navigation through Doctor workspace tabs</t>
-  </si>
-  <si>
-    <t>9:42:22 am</t>
-  </si>
-  <si>
-    <t>TC-7857</t>
-  </si>
-  <si>
-    <t>NAV-003: Validate navigation through Operations workspace tabs</t>
-  </si>
-  <si>
-    <t>9:42:34 am</t>
-  </si>
-  <si>
-    <t>TC-4744</t>
-  </si>
-  <si>
-    <t>NAV-004: Validate browser refresh, back, and forward navigation</t>
-  </si>
-  <si>
-    <t>9:42:45 am</t>
-  </si>
-  <si>
-    <t>TC-9789</t>
+    <t>TC-3316</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite</t>
@@ -304,48 +313,51 @@
     <t>UI-001: Validate Theme Toggle (Dark / Light mode)</t>
   </si>
   <si>
-    <t>9:42:52 am</t>
+    <t>9:16:00 pm</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>TC-7964</t>
+  </si>
+  <si>
+    <t>UI-002: Validate Language Selector Dropdown</t>
+  </si>
+  <si>
+    <t>9:16:02 pm</t>
+  </si>
+  <si>
+    <t>TC-4349</t>
+  </si>
+  <si>
+    <t>UI-003: Validate Forgot Password Modal open and close</t>
+  </si>
+  <si>
+    <t>9:16:10 pm</t>
+  </si>
+  <si>
+    <t>TC-4547</t>
+  </si>
+  <si>
+    <t>UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
+  </si>
+  <si>
+    <t>9:16:17 pm</t>
+  </si>
+  <si>
+    <t>TC-6480</t>
+  </si>
+  <si>
+    <t>UI-005: Validate Operations Doctor Verification Data Table and Review Modal</t>
+  </si>
+  <si>
+    <t>9:16:23 pm</t>
   </si>
   <si>
     <t>6s</t>
   </si>
   <si>
-    <t>TC-3275</t>
-  </si>
-  <si>
-    <t>UI-002: Validate Language Selector Dropdown</t>
-  </si>
-  <si>
-    <t>9:42:54 am</t>
-  </si>
-  <si>
-    <t>TC-7675</t>
-  </si>
-  <si>
-    <t>UI-003: Validate Forgot Password Modal open and close</t>
-  </si>
-  <si>
-    <t>9:43:05 am</t>
-  </si>
-  <si>
-    <t>TC-1870</t>
-  </si>
-  <si>
-    <t>UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
-  </si>
-  <si>
-    <t>9:43:18 am</t>
-  </si>
-  <si>
-    <t>TC-5093</t>
-  </si>
-  <si>
-    <t>UI-005: Validate Operations Doctor Verification Data Table and Review Modal</t>
-  </si>
-  <si>
-    <t>9:43:29 am</t>
-  </si>
-  <si>
     <t>Test Name</t>
   </si>
   <si>
@@ -358,299 +370,173 @@
     <t>URL</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>No failures recorded during execution. All tests passed successfully!</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Step Description</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:43:22</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Session Management Suite AUTH-001: Validate login with empty email field</t>
+  </si>
+  <si>
+    <t>Test Execution</t>
+  </si>
+  <si>
+    <t>Completed successfully</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:43:27</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Session Management Suite AUTH-002: Validate login with empty password field</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:43:31</t>
+  </si>
+  <si>
     <t>Authentication &amp; Session Management Suite AUTH-003: Validate login with invalid credentials</t>
   </si>
   <si>
-    <t>expected false to be true</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Authentication___Session_Management_Suite_AUTH-003__Validate_login_with_invalid_credentials_2026-08-03T04-09-59-389Z.png</t>
+    <t>2026-08-07 15:43:35</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-004: Validate successful Patient authentication flow</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10244ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Authentication___Session_Management_Suite_AUTH-004__Validate_successful_Patient_authentication_flow_2026-08-03T04-10-10-973Z.png</t>
+    <t>2026-08-07 15:43:40</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-005: Validate Patient logout flow</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10290ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Authentication___Session_Management_Suite_AUTH-005__Validate_Patient_logout_flow_2026-08-03T04-10-22-786Z.png</t>
+    <t>2026-08-07 15:43:48</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-006: Validate session persistence on page refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10279ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Authentication___Session_Management_Suite_AUTH-006__Validate_session_persistence_on_page_refresh_2026-08-03T04-10-34-566Z.png</t>
+    <t>2026-08-07 15:43:50</t>
+  </si>
+  <si>
+    <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-001: Validate discovered React routes configuration exists</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:44:06</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-002: Dynamic email input format validation on Signup form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Create account')])
-Wait timed out after 10269ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-002__Dynamic_email_input_format_validation_on_Signup_form_2026-08-03T04-10-47-403Z.png</t>
+    <t>2026-08-07 15:44:10</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Create account')])
-Wait timed out after 10290ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-003__Dynamic_password_mismatch_validation_on_Signup_form_2026-08-03T04-10-59-530Z.png</t>
+    <t>2026-08-07 15:44:18</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10286ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-004__Dynamic_validation_of_Patient_Symptom_Intake_form_2026-08-03T04-11-11-340Z.png</t>
+    <t>2026-08-07 15:44:26</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10277ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-005__Dynamic_validation_of_Doctor_Clinical_Notes_form_2026-08-03T04-11-23-064Z.png</t>
+    <t>2026-08-07 15:44:35</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10346ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-006__Dynamic_validation_of_Doctor_Prescription_Builder_form_2026-08-03T04-11-34-873Z.png</t>
+    <t>2026-08-07 15:44:46</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10240ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Dynamic_Form_Validation___Route_Discovery_Suite_FORM-DYN-007__Dynamic_validation_of_Operations_Hospital_ICU_form_2026-08-03T04-11-46-605Z.png</t>
+    <t>2026-08-07 15:45:24</t>
   </si>
   <si>
     <t>End-to-End Multi-Role Healthcare Workflow Suite E2E-001: Execute complete End-to-End patient consultation workflow</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10360ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_End-to-End_Multi-Role_Healthcare_Workflow_Suite_E2E-001__Execute_complete_End-to-End_patient_consultation_workflow_2026-08-03T04-11-58-356Z.png</t>
+    <t>2026-08-07 15:45:33</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-001: Validate navigation through all Patient workspace links</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10251ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Navigation___Internal_Routing_Validation_Suite_NAV-001__Validate_navigation_through_all_Patient_workspace_links_2026-08-03T04-12-10-085Z.png</t>
+    <t>2026-08-07 15:45:40</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-002: Validate navigation through Doctor workspace tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10332ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Navigation___Internal_Routing_Validation_Suite_NAV-002__Validate_navigation_through_Doctor_workspace_tabs_2026-08-03T04-12-22-011Z.png</t>
+    <t>2026-08-07 15:45:48</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-003: Validate navigation through Operations workspace tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10281ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Navigation___Internal_Routing_Validation_Suite_NAV-003__Validate_navigation_through_Operations_workspace_tabs_2026-08-03T04-12-33-753Z.png</t>
+    <t>2026-08-07 15:45:57</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-004: Validate browser refresh, back, and forward navigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10228ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_Navigation___Internal_Routing_Validation_Suite_NAV-004__Validate_browser_refresh__back__and_forward_navigation_2026-08-03T04-12-45-451Z.png</t>
+    <t>2026-08-07 15:46:00</t>
+  </si>
+  <si>
+    <t>UI &amp; Interactive Elements Validation Suite UI-001: Validate Theme Toggle (Dark / Light mode)</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:46:02</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-002: Validate Language Selector Dropdown</t>
   </si>
   <si>
-    <t xml:space="preserve">invalid element state
-  (Session info: chrome=151.0.7922.72)</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_UI___Interactive_Elements_Validation_Suite_UI-002__Validate_Language_Selector_Dropdown_2026-08-03T04-12-53-837Z.png</t>
+    <t>2026-08-07 15:46:10</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-003: Validate Forgot Password Modal open and close</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10253ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_UI___Interactive_Elements_Validation_Suite_UI-003__Validate_Forgot_Password_Modal_open_and_close_2026-08-03T04-13-05-583Z.png</t>
+    <t>2026-08-07 15:46:17</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10274ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_UI___Interactive_Elements_Validation_Suite_UI-004__Validate_Doctor_Search_Bar_filtering_in_Patient_Workspace_2026-08-03T04-13-17-643Z.png</t>
+    <t>2026-08-07 15:46:23</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-005: Validate Operations Doctor Verification Data Table and Review Modal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(@class, 'auth-tabs')]/button[contains(text(), 'Sign in')])
-Wait timed out after 10243ms</t>
-  </si>
-  <si>
-    <t>C:\Users\navee\Downloads\CareBridge-One-Naveen\carebridge-one\reports\failures\FAILURE_UI___Interactive_Elements_Validation_Suite_UI-005__Validate_Operations_Doctor_Verification_Data_Table_and_Review_Modal_2026-08-03T04-13-29-361Z.png</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Step Description</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:09:45</t>
-  </si>
-  <si>
-    <t>Authentication &amp; Session Management Suite AUTH-001: Validate login with empty email field</t>
-  </si>
-  <si>
-    <t>Test Execution</t>
-  </si>
-  <si>
-    <t>Completed successfully</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:09:49</t>
-  </si>
-  <si>
-    <t>Authentication &amp; Session Management Suite AUTH-002: Validate login with empty password field</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:09:59</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:11</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:23</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:34</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:36</t>
-  </si>
-  <si>
-    <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-001: Validate discovered React routes configuration exists</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:47</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:10:59</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:11:11</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:11:23</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:11:35</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:11:46</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:11:58</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:10</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:22</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:34</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:45</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:52</t>
-  </si>
-  <si>
-    <t>UI &amp; Interactive Elements Validation Suite UI-001: Validate Theme Toggle (Dark / Light mode)</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:12:54</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:13:05</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:13:18</t>
-  </si>
-  <si>
-    <t>2026-08-03 04:13:29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -667,12 +553,8 @@
       <b/>
       <color rgb="065F46"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="991B1B"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,11 +571,6 @@
         <fgColor rgb="D1FAE5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -707,13 +584,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,7 +989,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1121,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1258,251 +1134,251 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>39</v>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
-        <v>51</v>
-      </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
+      <c r="H8" t="s">
         <v>54</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="H9" t="s">
         <v>58</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
         <v>61</v>
       </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="H11" t="s">
         <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
         <v>68</v>
       </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" t="s">
-        <v>69</v>
-      </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
         <v>70</v>
       </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
         <v>71</v>
       </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>72</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1510,7 +1386,7 @@
         <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
         <v>74</v>
@@ -1518,277 +1394,277 @@
       <c r="D14" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>39</v>
+      <c r="E14" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
         <v>75</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>39</v>
+      <c r="E15" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
         <v>80</v>
       </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="s">
-        <v>83</v>
-      </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
         <v>88</v>
       </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" t="s">
-        <v>86</v>
-      </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
         <v>91</v>
       </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>89</v>
-      </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
         <v>94</v>
       </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>92</v>
-      </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
         <v>99</v>
       </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>39</v>
+      <c r="E22" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>39</v>
+      <c r="E23" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>39</v>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1811,341 +1687,35 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2169,152 +1739,152 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
         <v>127</v>
@@ -2322,257 +1892,257 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C23" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/excel/E2E_Report.xlsx
+++ b/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="171">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/8/2026, 9:16:23 pm</t>
+    <t>7/8/2026, 10:13:06 pm</t>
   </si>
   <si>
     <t>Environment</t>
@@ -67,7 +67,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>187 seconds</t>
+    <t>192 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -94,7 +94,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>TC-2809</t>
+    <t>TC-8378</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite</t>
@@ -106,256 +106,253 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>9:13:17 pm</t>
-  </si>
-  <si>
-    <t>9:13:22 pm</t>
+    <t>10:09:56 pm</t>
+  </si>
+  <si>
+    <t>10:10:02 pm</t>
+  </si>
+  <si>
+    <t>6s</t>
+  </si>
+  <si>
+    <t>TC-6430</t>
+  </si>
+  <si>
+    <t>AUTH-002: Validate login with empty password field</t>
+  </si>
+  <si>
+    <t>10:10:06 pm</t>
+  </si>
+  <si>
+    <t>4s</t>
+  </si>
+  <si>
+    <t>TC-3628</t>
+  </si>
+  <si>
+    <t>AUTH-003: Validate login with invalid credentials</t>
+  </si>
+  <si>
+    <t>10:10:10 pm</t>
+  </si>
+  <si>
+    <t>TC-3216</t>
+  </si>
+  <si>
+    <t>AUTH-004: Validate successful Patient authentication flow</t>
+  </si>
+  <si>
+    <t>10:10:15 pm</t>
   </si>
   <si>
     <t>5s</t>
   </si>
   <si>
-    <t>TC-8857</t>
-  </si>
-  <si>
-    <t>AUTH-002: Validate login with empty password field</t>
-  </si>
-  <si>
-    <t>9:13:27 pm</t>
-  </si>
-  <si>
-    <t>4s</t>
-  </si>
-  <si>
-    <t>TC-3871</t>
-  </si>
-  <si>
-    <t>AUTH-003: Validate login with invalid credentials</t>
-  </si>
-  <si>
-    <t>9:13:31 pm</t>
-  </si>
-  <si>
-    <t>TC-1785</t>
-  </si>
-  <si>
-    <t>AUTH-004: Validate successful Patient authentication flow</t>
-  </si>
-  <si>
-    <t>9:13:35 pm</t>
-  </si>
-  <si>
-    <t>TC-5624</t>
+    <t>TC-5860</t>
   </si>
   <si>
     <t>AUTH-005: Validate Patient logout flow</t>
   </si>
   <si>
-    <t>9:13:40 pm</t>
-  </si>
-  <si>
-    <t>TC-1156</t>
+    <t>10:10:21 pm</t>
+  </si>
+  <si>
+    <t>TC-8000</t>
   </si>
   <si>
     <t>AUTH-006: Validate session persistence on page refresh</t>
   </si>
   <si>
-    <t>9:13:48 pm</t>
+    <t>10:10:28 pm</t>
+  </si>
+  <si>
+    <t>8s</t>
+  </si>
+  <si>
+    <t>TC-7806</t>
+  </si>
+  <si>
+    <t>Dynamic Form Validation &amp; Route Discovery Suite</t>
+  </si>
+  <si>
+    <t>FORM-DYN-001: Validate discovered React routes configuration exists</t>
+  </si>
+  <si>
+    <t>10:10:30 pm</t>
+  </si>
+  <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>TC-2418</t>
+  </si>
+  <si>
+    <t>FORM-DYN-002: Dynamic email input format validation on Signup form</t>
+  </si>
+  <si>
+    <t>10:10:47 pm</t>
+  </si>
+  <si>
+    <t>17s</t>
+  </si>
+  <si>
+    <t>TC-1491</t>
+  </si>
+  <si>
+    <t>FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
+  </si>
+  <si>
+    <t>10:10:51 pm</t>
+  </si>
+  <si>
+    <t>TC-2380</t>
+  </si>
+  <si>
+    <t>FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
+  </si>
+  <si>
+    <t>10:10:59 pm</t>
+  </si>
+  <si>
+    <t>TC-6494</t>
+  </si>
+  <si>
+    <t>FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
+  </si>
+  <si>
+    <t>10:11:07 pm</t>
+  </si>
+  <si>
+    <t>TC-7378</t>
+  </si>
+  <si>
+    <t>FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
+  </si>
+  <si>
+    <t>10:11:16 pm</t>
+  </si>
+  <si>
+    <t>9s</t>
+  </si>
+  <si>
+    <t>TC-2445</t>
+  </si>
+  <si>
+    <t>FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
+  </si>
+  <si>
+    <t>10:11:27 pm</t>
+  </si>
+  <si>
+    <t>11s</t>
+  </si>
+  <si>
+    <t>TC-3626</t>
+  </si>
+  <si>
+    <t>End-to-End Multi-Role Healthcare Workflow Suite</t>
+  </si>
+  <si>
+    <t>E2E-001: Execute complete End-to-End patient consultation workflow</t>
+  </si>
+  <si>
+    <t>10:12:07 pm</t>
+  </si>
+  <si>
+    <t>39s</t>
+  </si>
+  <si>
+    <t>TC-9388</t>
+  </si>
+  <si>
+    <t>Navigation &amp; Internal Routing Validation Suite</t>
+  </si>
+  <si>
+    <t>NAV-001: Validate navigation through all Patient workspace links</t>
+  </si>
+  <si>
+    <t>10:12:15 pm</t>
+  </si>
+  <si>
+    <t>TC-6502</t>
+  </si>
+  <si>
+    <t>NAV-002: Validate navigation through Doctor workspace tabs</t>
+  </si>
+  <si>
+    <t>10:12:23 pm</t>
+  </si>
+  <si>
+    <t>TC-8049</t>
+  </si>
+  <si>
+    <t>NAV-003: Validate navigation through Operations workspace tabs</t>
+  </si>
+  <si>
+    <t>10:12:30 pm</t>
+  </si>
+  <si>
+    <t>TC-4845</t>
+  </si>
+  <si>
+    <t>NAV-004: Validate browser refresh, back, and forward navigation</t>
+  </si>
+  <si>
+    <t>10:12:39 pm</t>
+  </si>
+  <si>
+    <t>TC-1256</t>
+  </si>
+  <si>
+    <t>UI &amp; Interactive Elements Validation Suite</t>
+  </si>
+  <si>
+    <t>UI-001: Validate Theme Toggle (Dark / Light mode)</t>
+  </si>
+  <si>
+    <t>10:12:42 pm</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>TC-1232</t>
+  </si>
+  <si>
+    <t>UI-002: Validate Language Selector Dropdown</t>
+  </si>
+  <si>
+    <t>10:12:44 pm</t>
+  </si>
+  <si>
+    <t>TC-6884</t>
+  </si>
+  <si>
+    <t>UI-003: Validate Forgot Password Modal open and close</t>
+  </si>
+  <si>
+    <t>10:12:53 pm</t>
+  </si>
+  <si>
+    <t>TC-6956</t>
+  </si>
+  <si>
+    <t>UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
+  </si>
+  <si>
+    <t>10:12:59 pm</t>
   </si>
   <si>
     <t>7s</t>
   </si>
   <si>
-    <t>TC-8978</t>
-  </si>
-  <si>
-    <t>Dynamic Form Validation &amp; Route Discovery Suite</t>
-  </si>
-  <si>
-    <t>FORM-DYN-001: Validate discovered React routes configuration exists</t>
-  </si>
-  <si>
-    <t>9:13:50 pm</t>
-  </si>
-  <si>
-    <t>2s</t>
-  </si>
-  <si>
-    <t>TC-7147</t>
-  </si>
-  <si>
-    <t>FORM-DYN-002: Dynamic email input format validation on Signup form</t>
-  </si>
-  <si>
-    <t>9:14:06 pm</t>
-  </si>
-  <si>
-    <t>16s</t>
-  </si>
-  <si>
-    <t>TC-1589</t>
-  </si>
-  <si>
-    <t>FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
-  </si>
-  <si>
-    <t>9:14:10 pm</t>
-  </si>
-  <si>
-    <t>TC-7669</t>
-  </si>
-  <si>
-    <t>FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
-  </si>
-  <si>
-    <t>9:14:18 pm</t>
-  </si>
-  <si>
-    <t>8s</t>
-  </si>
-  <si>
-    <t>TC-7949</t>
-  </si>
-  <si>
-    <t>FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
-  </si>
-  <si>
-    <t>9:14:26 pm</t>
-  </si>
-  <si>
-    <t>TC-3681</t>
-  </si>
-  <si>
-    <t>FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
-  </si>
-  <si>
-    <t>9:14:35 pm</t>
-  </si>
-  <si>
-    <t>9s</t>
-  </si>
-  <si>
-    <t>TC-3095</t>
-  </si>
-  <si>
-    <t>FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
-  </si>
-  <si>
-    <t>9:14:46 pm</t>
-  </si>
-  <si>
-    <t>11s</t>
-  </si>
-  <si>
-    <t>TC-5947</t>
-  </si>
-  <si>
-    <t>End-to-End Multi-Role Healthcare Workflow Suite</t>
-  </si>
-  <si>
-    <t>E2E-001: Execute complete End-to-End patient consultation workflow</t>
-  </si>
-  <si>
-    <t>9:15:24 pm</t>
-  </si>
-  <si>
-    <t>38s</t>
-  </si>
-  <si>
-    <t>TC-1356</t>
-  </si>
-  <si>
-    <t>Navigation &amp; Internal Routing Validation Suite</t>
-  </si>
-  <si>
-    <t>NAV-001: Validate navigation through all Patient workspace links</t>
-  </si>
-  <si>
-    <t>9:15:33 pm</t>
-  </si>
-  <si>
-    <t>TC-5919</t>
-  </si>
-  <si>
-    <t>NAV-002: Validate navigation through Doctor workspace tabs</t>
-  </si>
-  <si>
-    <t>9:15:40 pm</t>
-  </si>
-  <si>
-    <t>TC-6737</t>
-  </si>
-  <si>
-    <t>NAV-003: Validate navigation through Operations workspace tabs</t>
-  </si>
-  <si>
-    <t>9:15:48 pm</t>
-  </si>
-  <si>
-    <t>TC-7552</t>
-  </si>
-  <si>
-    <t>NAV-004: Validate browser refresh, back, and forward navigation</t>
-  </si>
-  <si>
-    <t>9:15:57 pm</t>
-  </si>
-  <si>
-    <t>10s</t>
-  </si>
-  <si>
-    <t>TC-3316</t>
-  </si>
-  <si>
-    <t>UI &amp; Interactive Elements Validation Suite</t>
-  </si>
-  <si>
-    <t>UI-001: Validate Theme Toggle (Dark / Light mode)</t>
-  </si>
-  <si>
-    <t>9:16:00 pm</t>
-  </si>
-  <si>
-    <t>3s</t>
-  </si>
-  <si>
-    <t>TC-7964</t>
-  </si>
-  <si>
-    <t>UI-002: Validate Language Selector Dropdown</t>
-  </si>
-  <si>
-    <t>9:16:02 pm</t>
-  </si>
-  <si>
-    <t>TC-4349</t>
-  </si>
-  <si>
-    <t>UI-003: Validate Forgot Password Modal open and close</t>
-  </si>
-  <si>
-    <t>9:16:10 pm</t>
-  </si>
-  <si>
-    <t>TC-4547</t>
-  </si>
-  <si>
-    <t>UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
-  </si>
-  <si>
-    <t>9:16:17 pm</t>
-  </si>
-  <si>
-    <t>TC-6480</t>
+    <t>TC-6371</t>
   </si>
   <si>
     <t>UI-005: Validate Operations Doctor Verification Data Table and Review Modal</t>
   </si>
   <si>
-    <t>9:16:23 pm</t>
-  </si>
-  <si>
-    <t>6s</t>
+    <t>10:13:05 pm</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -388,7 +385,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:22</t>
+    <t>2026-08-07 16:40:02</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-001: Validate login with empty email field</t>
@@ -400,133 +397,133 @@
     <t>Completed successfully</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:27</t>
+    <t>2026-08-07 16:40:06</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-002: Validate login with empty password field</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:31</t>
+    <t>2026-08-07 16:40:10</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-003: Validate login with invalid credentials</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:35</t>
+    <t>2026-08-07 16:40:15</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-004: Validate successful Patient authentication flow</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:40</t>
+    <t>2026-08-07 16:40:21</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-005: Validate Patient logout flow</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:48</t>
+    <t>2026-08-07 16:40:28</t>
   </si>
   <si>
     <t>Authentication &amp; Session Management Suite AUTH-006: Validate session persistence on page refresh</t>
   </si>
   <si>
-    <t>2026-08-07 15:43:50</t>
+    <t>2026-08-07 16:40:30</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-001: Validate discovered React routes configuration exists</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:06</t>
+    <t>2026-08-07 16:40:47</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-002: Dynamic email input format validation on Signup form</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:10</t>
+    <t>2026-08-07 16:40:51</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-003: Dynamic password mismatch validation on Signup form</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:18</t>
+    <t>2026-08-07 16:40:59</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-004: Dynamic validation of Patient Symptom Intake form</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:26</t>
+    <t>2026-08-07 16:41:07</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-005: Dynamic validation of Doctor Clinical Notes form</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:35</t>
+    <t>2026-08-07 16:41:16</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-006: Dynamic validation of Doctor Prescription Builder form</t>
   </si>
   <si>
-    <t>2026-08-07 15:44:46</t>
+    <t>2026-08-07 16:41:27</t>
   </si>
   <si>
     <t>Dynamic Form Validation &amp; Route Discovery Suite FORM-DYN-007: Dynamic validation of Operations Hospital ICU form</t>
   </si>
   <si>
-    <t>2026-08-07 15:45:24</t>
+    <t>2026-08-07 16:42:07</t>
   </si>
   <si>
     <t>End-to-End Multi-Role Healthcare Workflow Suite E2E-001: Execute complete End-to-End patient consultation workflow</t>
   </si>
   <si>
-    <t>2026-08-07 15:45:33</t>
+    <t>2026-08-07 16:42:15</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-001: Validate navigation through all Patient workspace links</t>
   </si>
   <si>
-    <t>2026-08-07 15:45:40</t>
+    <t>2026-08-07 16:42:23</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-002: Validate navigation through Doctor workspace tabs</t>
   </si>
   <si>
-    <t>2026-08-07 15:45:48</t>
+    <t>2026-08-07 16:42:30</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-003: Validate navigation through Operations workspace tabs</t>
   </si>
   <si>
-    <t>2026-08-07 15:45:57</t>
+    <t>2026-08-07 16:42:39</t>
   </si>
   <si>
     <t>Navigation &amp; Internal Routing Validation Suite NAV-004: Validate browser refresh, back, and forward navigation</t>
   </si>
   <si>
-    <t>2026-08-07 15:46:00</t>
+    <t>2026-08-07 16:42:42</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-001: Validate Theme Toggle (Dark / Light mode)</t>
   </si>
   <si>
-    <t>2026-08-07 15:46:02</t>
+    <t>2026-08-07 16:42:44</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-002: Validate Language Selector Dropdown</t>
   </si>
   <si>
-    <t>2026-08-07 15:46:10</t>
+    <t>2026-08-07 16:42:53</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-003: Validate Forgot Password Modal open and close</t>
   </si>
   <si>
-    <t>2026-08-07 15:46:17</t>
+    <t>2026-08-07 16:42:59</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-004: Validate Doctor Search Bar filtering in Patient Workspace</t>
   </si>
   <si>
-    <t>2026-08-07 15:46:23</t>
+    <t>2026-08-07 16:43:05</t>
   </si>
   <si>
     <t>UI &amp; Interactive Elements Validation Suite UI-005: Validate Operations Doctor Verification Data Table and Review Modal</t>
@@ -1170,18 +1167,18 @@
         <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -1193,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
@@ -1201,13 +1198,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -1216,24 +1213,24 @@
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -1242,24 +1239,24 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -1268,24 +1265,24 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -1294,10 +1291,10 @@
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
         <v>36</v>
@@ -1305,28 +1302,28 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,7 +1331,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>67</v>
@@ -1346,13 +1343,13 @@
         <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
         <v>68</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1360,7 +1357,7 @@
         <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -1386,7 +1383,7 @@
         <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
         <v>74</v>
@@ -1456,7 +1453,7 @@
         <v>85</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1482,7 +1479,7 @@
         <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1508,7 +1505,7 @@
         <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1534,18 +1531,18 @@
         <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>97</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1557,88 +1554,88 @@
         <v>94</v>
       </c>
       <c r="G20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H20" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
         <v>102</v>
       </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" t="s">
-        <v>103</v>
-      </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" t="s">
         <v>105</v>
       </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>106</v>
-      </c>
       <c r="H22" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
         <v>107</v>
       </c>
-      <c r="B23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
         <v>108</v>
       </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>109</v>
-      </c>
-      <c r="H23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1646,7 +1643,7 @@
         <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
         <v>111</v>
@@ -1658,13 +1655,13 @@
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" t="s">
         <v>112</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1687,30 +1684,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" t="s">
-        <v>119</v>
-      </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1739,410 +1736,410 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s">
         <v>124</v>
       </c>
-      <c r="B2" t="s">
-        <v>125</v>
-      </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
         <v>128</v>
       </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
         <v>130</v>
       </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
         <v>132</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
         <v>134</v>
       </c>
-      <c r="B6" t="s">
-        <v>135</v>
-      </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
         <v>136</v>
       </c>
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
         <v>138</v>
       </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" t="s">
         <v>140</v>
       </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
         <v>142</v>
       </c>
-      <c r="B10" t="s">
-        <v>143</v>
-      </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="s">
         <v>144</v>
       </c>
-      <c r="B11" t="s">
-        <v>145</v>
-      </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" t="s">
         <v>146</v>
       </c>
-      <c r="B12" t="s">
-        <v>147</v>
-      </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" t="s">
         <v>148</v>
       </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" t="s">
         <v>150</v>
       </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
         <v>152</v>
       </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" t="s">
         <v>154</v>
       </c>
-      <c r="B16" t="s">
-        <v>155</v>
-      </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" t="s">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
-        <v>157</v>
-      </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" t="s">
         <v>158</v>
       </c>
-      <c r="B18" t="s">
-        <v>159</v>
-      </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" t="s">
         <v>160</v>
       </c>
-      <c r="B19" t="s">
-        <v>161</v>
-      </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" t="s">
         <v>162</v>
       </c>
-      <c r="B20" t="s">
-        <v>163</v>
-      </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" t="s">
         <v>164</v>
       </c>
-      <c r="B21" t="s">
-        <v>165</v>
-      </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" t="s">
         <v>166</v>
       </c>
-      <c r="B22" t="s">
-        <v>167</v>
-      </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" t="s">
         <v>168</v>
       </c>
-      <c r="B23" t="s">
-        <v>169</v>
-      </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" t="s">
         <v>170</v>
       </c>
-      <c r="B24" t="s">
-        <v>171</v>
-      </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
